--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175489</v>
+        <v>120175887</v>
       </c>
       <c r="B2" t="n">
-        <v>56514</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582599</v>
+        <v>582692</v>
       </c>
       <c r="R2" t="n">
-        <v>7025970</v>
+        <v>7026050</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176305</v>
+        <v>120176065</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582645</v>
+        <v>582672</v>
       </c>
       <c r="R3" t="n">
-        <v>7026059</v>
+        <v>7026027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +860,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120175885</v>
+        <v>120177315</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582678</v>
+        <v>582517</v>
       </c>
       <c r="R4" t="n">
-        <v>7026025</v>
+        <v>7026141</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120176525</v>
+        <v>120175900</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582518</v>
+        <v>582678</v>
       </c>
       <c r="R5" t="n">
-        <v>7026110</v>
+        <v>7026025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175584</v>
+        <v>120175741</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>79511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582645</v>
+        <v>582661</v>
       </c>
       <c r="R6" t="n">
-        <v>7025976</v>
+        <v>7026021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,24 +1166,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120176085</v>
+        <v>120175885</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,47 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582532</v>
+        <v>582678</v>
       </c>
       <c r="R7" t="n">
-        <v>7026064</v>
+        <v>7026025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,19 +1268,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120175644</v>
+        <v>120176600</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>90573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582635</v>
+        <v>582505</v>
       </c>
       <c r="R8" t="n">
-        <v>7025986</v>
+        <v>7026082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,21 +1383,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120175741</v>
+        <v>120176525</v>
       </c>
       <c r="B9" t="n">
-        <v>79511</v>
+        <v>79636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582661</v>
+        <v>582518</v>
       </c>
       <c r="R9" t="n">
-        <v>7026021</v>
+        <v>7026110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120175900</v>
+        <v>120175748</v>
       </c>
       <c r="B10" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582678</v>
+        <v>582659</v>
       </c>
       <c r="R10" t="n">
-        <v>7026025</v>
+        <v>7026084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,9 +1574,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120175892</v>
+        <v>120176305</v>
       </c>
       <c r="B11" t="n">
-        <v>79567</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,38 +1625,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582678</v>
+        <v>582645</v>
       </c>
       <c r="R11" t="n">
-        <v>7026025</v>
+        <v>7026059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,9 +1691,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,19 +1718,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176323</v>
+        <v>120176514</v>
       </c>
       <c r="B12" t="n">
         <v>79607</v>
@@ -1819,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582522</v>
+        <v>582518</v>
       </c>
       <c r="R12" t="n">
-        <v>7026104</v>
+        <v>7026110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,19 +1803,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,22 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120176679</v>
+        <v>120175584</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,30 +1844,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1935,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582480</v>
+        <v>582645</v>
       </c>
       <c r="R13" t="n">
-        <v>7026053</v>
+        <v>7025976</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1922,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175484</v>
+        <v>120175489</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>56514</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,31 +1970,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2056,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582617</v>
+        <v>582599</v>
       </c>
       <c r="R14" t="n">
-        <v>7025987</v>
+        <v>7025970</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,22 +2059,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176514</v>
+        <v>120175484</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,37 +2087,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582518</v>
+        <v>582617</v>
       </c>
       <c r="R15" t="n">
-        <v>7026110</v>
+        <v>7025987</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,9 +2153,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176505</v>
+        <v>120176322</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,42 +2204,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582527</v>
+        <v>582663</v>
       </c>
       <c r="R16" t="n">
-        <v>7026102</v>
+        <v>7026088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,19 +2265,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,22 +2282,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120176600</v>
+        <v>120177433</v>
       </c>
       <c r="B17" t="n">
-        <v>90573</v>
+        <v>74577</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2386,13 +2334,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582505</v>
+        <v>582517</v>
       </c>
       <c r="R17" t="n">
-        <v>7026082</v>
+        <v>7026141</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176065</v>
+        <v>120175644</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582672</v>
+        <v>582635</v>
       </c>
       <c r="R18" t="n">
-        <v>7026027</v>
+        <v>7025986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,6 +2482,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2550,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120176322</v>
+        <v>120176505</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2562,38 +2525,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582663</v>
+        <v>582527</v>
       </c>
       <c r="R19" t="n">
-        <v>7026088</v>
+        <v>7026102</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,9 +2590,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2640,12 +2617,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2764,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120175887</v>
+        <v>120175892</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2776,25 +2753,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2804,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582692</v>
+        <v>582678</v>
       </c>
       <c r="R21" t="n">
-        <v>7026050</v>
+        <v>7026025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,19 +2814,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,22 +2831,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120176536</v>
+        <v>120176679</v>
       </c>
       <c r="B22" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2888,38 +2855,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582505</v>
+        <v>582480</v>
       </c>
       <c r="R22" t="n">
-        <v>7026082</v>
+        <v>7026053</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,9 +2920,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,22 +2947,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120177315</v>
+        <v>120176257</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,25 +2971,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3018,13 +2999,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582517</v>
+        <v>582663</v>
       </c>
       <c r="R23" t="n">
-        <v>7026141</v>
+        <v>7026088</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3080,10 +3061,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120176257</v>
+        <v>120176536</v>
       </c>
       <c r="B24" t="n">
-        <v>79567</v>
+        <v>94311</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3096,21 +3077,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3120,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582663</v>
+        <v>582505</v>
       </c>
       <c r="R24" t="n">
-        <v>7026088</v>
+        <v>7026082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,7 +3163,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120175748</v>
+        <v>120176323</v>
       </c>
       <c r="B25" t="n">
         <v>79607</v>
@@ -3222,10 +3203,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582659</v>
+        <v>582522</v>
       </c>
       <c r="R25" t="n">
-        <v>7026084</v>
+        <v>7026104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3238,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3267,7 +3248,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,10 +3275,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120177433</v>
+        <v>120176085</v>
       </c>
       <c r="B26" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,41 +3287,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582517</v>
+        <v>582532</v>
       </c>
       <c r="R26" t="n">
-        <v>7026141</v>
+        <v>7026064</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3367,9 +3357,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,12 +3384,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175741</v>
+        <v>120175885</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582661</v>
+        <v>582678</v>
       </c>
       <c r="R6" t="n">
-        <v>7026021</v>
+        <v>7026025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175885</v>
+        <v>120175741</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R7" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176600</v>
+        <v>120176525</v>
       </c>
       <c r="B8" t="n">
-        <v>90573</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R8" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176525</v>
+        <v>120175748</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582518</v>
+        <v>582659</v>
       </c>
       <c r="R9" t="n">
-        <v>7026110</v>
+        <v>7026084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,9 +1472,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120175748</v>
+        <v>120176305</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582659</v>
+        <v>582645</v>
       </c>
       <c r="R10" t="n">
-        <v>7026084</v>
+        <v>7026059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1616,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176305</v>
+        <v>120176600</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>90573</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,43 +1640,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582645</v>
+        <v>582505</v>
       </c>
       <c r="R11" t="n">
-        <v>7026059</v>
+        <v>7026082</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,19 +1701,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,12 +1718,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175489</v>
+        <v>120175484</v>
       </c>
       <c r="B14" t="n">
-        <v>56514</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,27 +1970,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1999,13 +2003,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582599</v>
+        <v>582617</v>
       </c>
       <c r="R14" t="n">
-        <v>7025970</v>
+        <v>7025987</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175484</v>
+        <v>120176322</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,50 +2087,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582617</v>
+        <v>582663</v>
       </c>
       <c r="R15" t="n">
-        <v>7025987</v>
+        <v>7026088</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,19 +2148,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2165,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176322</v>
+        <v>120175489</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>56514</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,38 +2189,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582663</v>
+        <v>582599</v>
       </c>
       <c r="R16" t="n">
-        <v>7026088</v>
+        <v>7025970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,9 +2255,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,12 +2282,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175885</v>
+        <v>120175741</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R6" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175741</v>
+        <v>120175885</v>
       </c>
       <c r="B7" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582661</v>
+        <v>582678</v>
       </c>
       <c r="R7" t="n">
-        <v>7026021</v>
+        <v>7026025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176525</v>
+        <v>120176600</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>90573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582518</v>
+        <v>582505</v>
       </c>
       <c r="R8" t="n">
-        <v>7026110</v>
+        <v>7026082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120175748</v>
+        <v>120176525</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582659</v>
+        <v>582518</v>
       </c>
       <c r="R9" t="n">
-        <v>7026084</v>
+        <v>7026110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,19 +1472,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176305</v>
+        <v>120175748</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1517,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582645</v>
+        <v>582659</v>
       </c>
       <c r="R10" t="n">
-        <v>7026059</v>
+        <v>7026084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1576,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1601,7 +1586,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176600</v>
+        <v>120176305</v>
       </c>
       <c r="B11" t="n">
-        <v>90573</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,38 +1625,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582505</v>
+        <v>582645</v>
       </c>
       <c r="R11" t="n">
-        <v>7026082</v>
+        <v>7026059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,9 +1691,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,12 +1718,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175484</v>
+        <v>120175489</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>56514</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,31 +1970,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2003,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582617</v>
+        <v>582599</v>
       </c>
       <c r="R14" t="n">
-        <v>7025987</v>
+        <v>7025970</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,22 +2059,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176322</v>
+        <v>120175484</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,41 +2083,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582663</v>
+        <v>582617</v>
       </c>
       <c r="R15" t="n">
-        <v>7026088</v>
+        <v>7025987</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,9 +2153,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175489</v>
+        <v>120176322</v>
       </c>
       <c r="B16" t="n">
-        <v>56514</v>
+        <v>79636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,43 +2204,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582599</v>
+        <v>582663</v>
       </c>
       <c r="R16" t="n">
-        <v>7025970</v>
+        <v>7026088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,19 +2265,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,12 +2282,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176600</v>
+        <v>120176525</v>
       </c>
       <c r="B8" t="n">
-        <v>90573</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R8" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176525</v>
+        <v>120175748</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582518</v>
+        <v>582659</v>
       </c>
       <c r="R9" t="n">
-        <v>7026110</v>
+        <v>7026084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,9 +1472,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120175748</v>
+        <v>120176305</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582659</v>
+        <v>582645</v>
       </c>
       <c r="R10" t="n">
-        <v>7026084</v>
+        <v>7026059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1586,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1616,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176305</v>
+        <v>120176600</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>90573</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,43 +1640,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582645</v>
+        <v>582505</v>
       </c>
       <c r="R11" t="n">
-        <v>7026059</v>
+        <v>7026082</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,19 +1701,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,12 +1718,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175489</v>
+        <v>120175484</v>
       </c>
       <c r="B14" t="n">
-        <v>56514</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,27 +1970,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1999,13 +2003,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582599</v>
+        <v>582617</v>
       </c>
       <c r="R14" t="n">
-        <v>7025970</v>
+        <v>7025987</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175484</v>
+        <v>120176322</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,50 +2087,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582617</v>
+        <v>582663</v>
       </c>
       <c r="R15" t="n">
-        <v>7025987</v>
+        <v>7026088</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,19 +2148,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,22 +2165,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176322</v>
+        <v>120175489</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>56514</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,38 +2189,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582663</v>
+        <v>582599</v>
       </c>
       <c r="R16" t="n">
-        <v>7026088</v>
+        <v>7025970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,9 +2255,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,12 +2282,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175741</v>
+        <v>120175885</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582661</v>
+        <v>582678</v>
       </c>
       <c r="R6" t="n">
-        <v>7026021</v>
+        <v>7026025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175885</v>
+        <v>120175741</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R7" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175484</v>
+        <v>120176322</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,50 +1966,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582617</v>
+        <v>582663</v>
       </c>
       <c r="R14" t="n">
-        <v>7025987</v>
+        <v>7026088</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2036,19 +2027,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,22 +2044,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176322</v>
+        <v>120175489</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>56514</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,38 +2068,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582663</v>
+        <v>582599</v>
       </c>
       <c r="R15" t="n">
-        <v>7026088</v>
+        <v>7025970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,9 +2134,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,22 +2161,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175489</v>
+        <v>120175484</v>
       </c>
       <c r="B16" t="n">
-        <v>56514</v>
+        <v>57463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,27 +2189,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582599</v>
+        <v>582617</v>
       </c>
       <c r="R16" t="n">
-        <v>7025970</v>
+        <v>7025987</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,12 +2282,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175885</v>
+        <v>120175741</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R6" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175741</v>
+        <v>120175885</v>
       </c>
       <c r="B7" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582661</v>
+        <v>582678</v>
       </c>
       <c r="R7" t="n">
-        <v>7026021</v>
+        <v>7026025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175887</v>
+        <v>120177315</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582692</v>
+        <v>582517</v>
       </c>
       <c r="R2" t="n">
-        <v>7026050</v>
+        <v>7026141</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176065</v>
+        <v>120176323</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582672</v>
+        <v>582522</v>
       </c>
       <c r="R3" t="n">
-        <v>7026027</v>
+        <v>7026104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,9 +850,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120177315</v>
+        <v>120176085</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +901,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582517</v>
+        <v>582532</v>
       </c>
       <c r="R4" t="n">
-        <v>7026141</v>
+        <v>7026064</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,9 +971,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120175900</v>
+        <v>120175484</v>
       </c>
       <c r="B5" t="n">
-        <v>79511</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,41 +1022,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582678</v>
+        <v>582617</v>
       </c>
       <c r="R5" t="n">
-        <v>7026025</v>
+        <v>7025987</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1092,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175741</v>
+        <v>120176305</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1143,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582661</v>
+        <v>582645</v>
       </c>
       <c r="R6" t="n">
-        <v>7026021</v>
+        <v>7026059</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,9 +1209,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175885</v>
+        <v>120175584</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1264,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582678</v>
+        <v>582645</v>
       </c>
       <c r="R7" t="n">
-        <v>7026025</v>
+        <v>7025976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,9 +1326,24 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,22 +1358,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176525</v>
+        <v>120175887</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1382,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582518</v>
+        <v>582692</v>
       </c>
       <c r="R8" t="n">
-        <v>7026110</v>
+        <v>7026050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,9 +1443,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120175748</v>
+        <v>120176525</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1494,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582659</v>
+        <v>582518</v>
       </c>
       <c r="R9" t="n">
-        <v>7026084</v>
+        <v>7026110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,19 +1555,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,22 +1572,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176305</v>
+        <v>120176505</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,31 +1596,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1556,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582645</v>
+        <v>582527</v>
       </c>
       <c r="R10" t="n">
-        <v>7026059</v>
+        <v>7026102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1601,7 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176600</v>
+        <v>120175885</v>
       </c>
       <c r="B11" t="n">
-        <v>90573</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,25 +1712,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582505</v>
+        <v>582678</v>
       </c>
       <c r="R11" t="n">
-        <v>7026082</v>
+        <v>7026025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176514</v>
+        <v>120176257</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>79583</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1814,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582518</v>
+        <v>582663</v>
       </c>
       <c r="R12" t="n">
-        <v>7026110</v>
+        <v>7026088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120175584</v>
+        <v>120176536</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>94334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,43 +1916,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582645</v>
+        <v>582505</v>
       </c>
       <c r="R13" t="n">
-        <v>7025976</v>
+        <v>7026082</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,24 +1977,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,22 +1994,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120176322</v>
+        <v>120176514</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +2018,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582663</v>
+        <v>582518</v>
       </c>
       <c r="R14" t="n">
-        <v>7026088</v>
+        <v>7026110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175489</v>
+        <v>120176065</v>
       </c>
       <c r="B15" t="n">
-        <v>56514</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,43 +2120,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582599</v>
+        <v>582672</v>
       </c>
       <c r="R15" t="n">
-        <v>7025970</v>
+        <v>7026027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,19 +2181,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,22 +2198,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175484</v>
+        <v>120175489</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>56524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,31 +2226,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2222,13 +2255,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582617</v>
+        <v>582599</v>
       </c>
       <c r="R16" t="n">
-        <v>7025987</v>
+        <v>7025970</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2257,7 +2290,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2300,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,22 +2315,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120177433</v>
+        <v>120177419</v>
       </c>
       <c r="B17" t="n">
-        <v>74577</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,13 +2367,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582517</v>
+        <v>582515</v>
       </c>
       <c r="R17" t="n">
-        <v>7026141</v>
+        <v>7026157</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2367,9 +2400,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,22 +2427,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120175644</v>
+        <v>120176322</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2451,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582635</v>
+        <v>582663</v>
       </c>
       <c r="R18" t="n">
-        <v>7025986</v>
+        <v>7026088</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,21 +2525,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2513,10 +2541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120176505</v>
+        <v>120175748</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,42 +2553,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582527</v>
+        <v>582659</v>
       </c>
       <c r="R19" t="n">
-        <v>7026102</v>
+        <v>7026084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2616,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2602,7 +2626,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,22 +2641,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120177419</v>
+        <v>120175644</v>
       </c>
       <c r="B20" t="n">
-        <v>82305</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2669,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582515</v>
+        <v>582635</v>
       </c>
       <c r="R20" t="n">
-        <v>7026157</v>
+        <v>7025986</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,21 +2726,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2725,26 +2739,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120175892</v>
+        <v>120175741</v>
       </c>
       <c r="B21" t="n">
-        <v>79567</v>
+        <v>79527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,21 +2786,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R21" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,7 +2875,7 @@
         <v>120176679</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2959,10 +2988,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120176257</v>
+        <v>120175900</v>
       </c>
       <c r="B23" t="n">
-        <v>79567</v>
+        <v>79527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,21 +3004,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2999,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582663</v>
+        <v>582678</v>
       </c>
       <c r="R23" t="n">
-        <v>7026088</v>
+        <v>7026025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,10 +3090,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120176536</v>
+        <v>120177433</v>
       </c>
       <c r="B24" t="n">
-        <v>94311</v>
+        <v>74593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3077,21 +3106,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3101,13 +3130,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582505</v>
+        <v>582517</v>
       </c>
       <c r="R24" t="n">
-        <v>7026082</v>
+        <v>7026141</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3163,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120176323</v>
+        <v>120175892</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>79583</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3175,25 +3204,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3203,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582522</v>
+        <v>582678</v>
       </c>
       <c r="R25" t="n">
-        <v>7026104</v>
+        <v>7026025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,19 +3265,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,22 +3282,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176085</v>
+        <v>120176600</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>90591</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3287,47 +3306,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582532</v>
+        <v>582505</v>
       </c>
       <c r="R26" t="n">
-        <v>7026064</v>
+        <v>7026082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,19 +3367,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,12 +3384,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120176536</v>
+        <v>120176514</v>
       </c>
       <c r="B13" t="n">
-        <v>94334</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R13" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120176514</v>
+        <v>120176065</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582518</v>
+        <v>582672</v>
       </c>
       <c r="R14" t="n">
-        <v>7026110</v>
+        <v>7026027</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176065</v>
+        <v>120176536</v>
       </c>
       <c r="B15" t="n">
-        <v>79652</v>
+        <v>94334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582672</v>
+        <v>582505</v>
       </c>
       <c r="R15" t="n">
-        <v>7026027</v>
+        <v>7026082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120177315</v>
+        <v>120176505</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582517</v>
+        <v>582527</v>
       </c>
       <c r="R2" t="n">
-        <v>7026141</v>
+        <v>7026102</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +752,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176323</v>
+        <v>120176525</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582522</v>
+        <v>582518</v>
       </c>
       <c r="R3" t="n">
-        <v>7026104</v>
+        <v>7026110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +864,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120176085</v>
+        <v>120176323</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,47 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582532</v>
+        <v>582522</v>
       </c>
       <c r="R4" t="n">
-        <v>7026064</v>
+        <v>7026104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120175484</v>
+        <v>120177419</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,46 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582617</v>
+        <v>582515</v>
       </c>
       <c r="R5" t="n">
-        <v>7025987</v>
+        <v>7026157</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120176305</v>
+        <v>120175900</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>79527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,43 +1129,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582645</v>
+        <v>582678</v>
       </c>
       <c r="R6" t="n">
-        <v>7026059</v>
+        <v>7026025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,19 +1190,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175584</v>
+        <v>120175489</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,16 +1235,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1284,7 +1255,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582645</v>
+        <v>582599</v>
       </c>
       <c r="R7" t="n">
-        <v>7025976</v>
+        <v>7025970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120175887</v>
+        <v>120175484</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,37 +1352,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582692</v>
+        <v>582617</v>
       </c>
       <c r="R8" t="n">
-        <v>7026050</v>
+        <v>7025987</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176525</v>
+        <v>120176679</v>
       </c>
       <c r="B9" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1469,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582518</v>
+        <v>582480</v>
       </c>
       <c r="R9" t="n">
-        <v>7026110</v>
+        <v>7026053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,9 +1534,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,22 +1561,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176505</v>
+        <v>120176514</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,42 +1585,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582527</v>
+        <v>582518</v>
       </c>
       <c r="R10" t="n">
-        <v>7026102</v>
+        <v>7026110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,19 +1646,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1663,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120175885</v>
+        <v>120176536</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582678</v>
+        <v>582505</v>
       </c>
       <c r="R11" t="n">
-        <v>7026025</v>
+        <v>7026082</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176257</v>
+        <v>120175584</v>
       </c>
       <c r="B12" t="n">
-        <v>79583</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,38 +1789,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582663</v>
+        <v>582645</v>
       </c>
       <c r="R12" t="n">
-        <v>7026088</v>
+        <v>7025976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,9 +1855,24 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,19 +1887,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120176514</v>
+        <v>120175885</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582518</v>
+        <v>582678</v>
       </c>
       <c r="R13" t="n">
-        <v>7026110</v>
+        <v>7026025</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120176065</v>
+        <v>120176257</v>
       </c>
       <c r="B14" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582672</v>
+        <v>582663</v>
       </c>
       <c r="R14" t="n">
-        <v>7026027</v>
+        <v>7026088</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176536</v>
+        <v>120175644</v>
       </c>
       <c r="B15" t="n">
-        <v>94334</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582505</v>
+        <v>582635</v>
       </c>
       <c r="R15" t="n">
-        <v>7026082</v>
+        <v>7025986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,6 +2189,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2210,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175489</v>
+        <v>120176085</v>
       </c>
       <c r="B16" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,31 +2232,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2255,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582599</v>
+        <v>582532</v>
       </c>
       <c r="R16" t="n">
-        <v>7025970</v>
+        <v>7026064</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2300,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,22 +2329,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120177419</v>
+        <v>120177433</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>74593</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2353,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,13 +2381,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582515</v>
+        <v>582517</v>
       </c>
       <c r="R17" t="n">
-        <v>7026157</v>
+        <v>7026141</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2400,19 +2414,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,22 +2431,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176322</v>
+        <v>120175892</v>
       </c>
       <c r="B18" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2455,21 +2459,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2483,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582663</v>
+        <v>582678</v>
       </c>
       <c r="R18" t="n">
-        <v>7026088</v>
+        <v>7026025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120175748</v>
+        <v>120177315</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,21 +2561,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2581,13 +2585,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582659</v>
+        <v>582517</v>
       </c>
       <c r="R19" t="n">
-        <v>7026084</v>
+        <v>7026141</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2614,19 +2618,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,22 +2635,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120175644</v>
+        <v>120175741</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>79527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,25 +2659,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582635</v>
+        <v>582661</v>
       </c>
       <c r="R20" t="n">
-        <v>7025986</v>
+        <v>7026021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,21 +2733,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2770,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120175741</v>
+        <v>120176065</v>
       </c>
       <c r="B21" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,21 +2765,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2810,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582661</v>
+        <v>582672</v>
       </c>
       <c r="R21" t="n">
-        <v>7026021</v>
+        <v>7026027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120176679</v>
+        <v>120176600</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90591</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2884,42 +2863,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582480</v>
+        <v>582505</v>
       </c>
       <c r="R22" t="n">
-        <v>7026053</v>
+        <v>7026082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,19 +2924,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2976,22 +2941,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120175900</v>
+        <v>120176305</v>
       </c>
       <c r="B23" t="n">
-        <v>79527</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,38 +2965,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582678</v>
+        <v>582645</v>
       </c>
       <c r="R23" t="n">
-        <v>7026025</v>
+        <v>7026059</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,9 +3031,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,22 +3058,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120177433</v>
+        <v>120175748</v>
       </c>
       <c r="B24" t="n">
-        <v>74593</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,25 +3082,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3130,13 +3110,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582517</v>
+        <v>582659</v>
       </c>
       <c r="R24" t="n">
-        <v>7026141</v>
+        <v>7026084</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3163,9 +3143,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,22 +3170,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120175892</v>
+        <v>120175887</v>
       </c>
       <c r="B25" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,25 +3194,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582678</v>
+        <v>582692</v>
       </c>
       <c r="R25" t="n">
-        <v>7026025</v>
+        <v>7026050</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,9 +3255,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,22 +3282,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176600</v>
+        <v>120176322</v>
       </c>
       <c r="B26" t="n">
-        <v>90591</v>
+        <v>79652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582505</v>
+        <v>582663</v>
       </c>
       <c r="R26" t="n">
-        <v>7026082</v>
+        <v>7026088</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120177419</v>
+        <v>120175900</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>79527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582515</v>
+        <v>582678</v>
       </c>
       <c r="R5" t="n">
-        <v>7026157</v>
+        <v>7026025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1078,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1095,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175900</v>
+        <v>120177419</v>
       </c>
       <c r="B6" t="n">
-        <v>79527</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582678</v>
+        <v>582515</v>
       </c>
       <c r="R6" t="n">
-        <v>7026025</v>
+        <v>7026157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,9 +1180,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120176505</v>
+        <v>120176536</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>94334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582527</v>
+        <v>582505</v>
       </c>
       <c r="R2" t="n">
-        <v>7026102</v>
+        <v>7026082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +748,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176525</v>
+        <v>120176322</v>
       </c>
       <c r="B3" t="n">
         <v>79652</v>
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582518</v>
+        <v>582663</v>
       </c>
       <c r="R3" t="n">
-        <v>7026110</v>
+        <v>7026088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120176323</v>
+        <v>120175484</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,37 +895,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582522</v>
+        <v>582617</v>
       </c>
       <c r="R4" t="n">
-        <v>7026104</v>
+        <v>7025987</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120175900</v>
+        <v>120176305</v>
       </c>
       <c r="B5" t="n">
-        <v>79527</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,38 +1012,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582678</v>
+        <v>582645</v>
       </c>
       <c r="R5" t="n">
-        <v>7026025</v>
+        <v>7026059</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,9 +1078,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120177419</v>
+        <v>120175741</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>79527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582515</v>
+        <v>582661</v>
       </c>
       <c r="R6" t="n">
-        <v>7026157</v>
+        <v>7026021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,19 +1190,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175489</v>
+        <v>120175900</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
+        <v>79527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,43 +1231,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582599</v>
+        <v>582678</v>
       </c>
       <c r="R7" t="n">
-        <v>7025970</v>
+        <v>7026025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,19 +1292,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1309,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120175484</v>
+        <v>120176525</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>79652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,50 +1333,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582617</v>
+        <v>582518</v>
       </c>
       <c r="R8" t="n">
-        <v>7025987</v>
+        <v>7026110</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,19 +1394,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,19 +1411,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176679</v>
+        <v>120176085</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1492,7 +1458,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1501,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582480</v>
+        <v>582532</v>
       </c>
       <c r="R9" t="n">
-        <v>7026053</v>
+        <v>7026064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1532,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176514</v>
+        <v>120176600</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>90591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582518</v>
+        <v>582505</v>
       </c>
       <c r="R10" t="n">
-        <v>7026110</v>
+        <v>7026082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176536</v>
+        <v>120177419</v>
       </c>
       <c r="B11" t="n">
-        <v>94334</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582505</v>
+        <v>582515</v>
       </c>
       <c r="R11" t="n">
-        <v>7026082</v>
+        <v>7026157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,9 +1719,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1746,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120175584</v>
+        <v>120176323</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,39 +1774,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582645</v>
+        <v>582522</v>
       </c>
       <c r="R12" t="n">
-        <v>7025976</v>
+        <v>7026104</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1833,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,12 +1843,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1858,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120175885</v>
+        <v>120177433</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>74593</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,25 +1882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1939,13 +1910,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582678</v>
+        <v>582517</v>
       </c>
       <c r="R13" t="n">
-        <v>7026025</v>
+        <v>7026141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120176257</v>
+        <v>120175885</v>
       </c>
       <c r="B14" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582663</v>
+        <v>582678</v>
       </c>
       <c r="R14" t="n">
-        <v>7026088</v>
+        <v>7026025</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2220,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176085</v>
+        <v>120175489</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,35 +2203,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2269,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582532</v>
+        <v>582599</v>
       </c>
       <c r="R16" t="n">
-        <v>7026064</v>
+        <v>7025970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2314,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,22 +2296,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120177433</v>
+        <v>120176679</v>
       </c>
       <c r="B17" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,41 +2320,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582517</v>
+        <v>582480</v>
       </c>
       <c r="R17" t="n">
-        <v>7026141</v>
+        <v>7026053</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,9 +2385,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,19 +2412,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120175892</v>
+        <v>120176257</v>
       </c>
       <c r="B18" t="n">
         <v>79583</v>
@@ -2483,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582678</v>
+        <v>582663</v>
       </c>
       <c r="R18" t="n">
-        <v>7026025</v>
+        <v>7026088</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,10 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120177315</v>
+        <v>120175748</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,21 +2542,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2585,13 +2566,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582517</v>
+        <v>582659</v>
       </c>
       <c r="R19" t="n">
-        <v>7026141</v>
+        <v>7026084</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,9 +2599,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,22 +2626,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120175741</v>
+        <v>120175887</v>
       </c>
       <c r="B20" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,25 +2650,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2687,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582661</v>
+        <v>582692</v>
       </c>
       <c r="R20" t="n">
-        <v>7026021</v>
+        <v>7026050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,9 +2711,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,22 +2738,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120176065</v>
+        <v>120176505</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,38 +2762,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582672</v>
+        <v>582527</v>
       </c>
       <c r="R21" t="n">
-        <v>7026027</v>
+        <v>7026102</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,9 +2827,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,22 +2854,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120176600</v>
+        <v>120175892</v>
       </c>
       <c r="B22" t="n">
-        <v>90591</v>
+        <v>79583</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2891,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582505</v>
+        <v>582678</v>
       </c>
       <c r="R22" t="n">
-        <v>7026082</v>
+        <v>7026025</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2953,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120176305</v>
+        <v>120176065</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,43 +2980,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582645</v>
+        <v>582672</v>
       </c>
       <c r="R23" t="n">
-        <v>7026059</v>
+        <v>7026027</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,19 +3041,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,22 +3058,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120175748</v>
+        <v>120177315</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582659</v>
+        <v>582517</v>
       </c>
       <c r="R24" t="n">
-        <v>7026084</v>
+        <v>7026141</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3143,19 +3143,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,22 +3160,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120175887</v>
+        <v>120175584</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3198,34 +3188,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582692</v>
+        <v>582645</v>
       </c>
       <c r="R25" t="n">
-        <v>7026050</v>
+        <v>7025976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3267,7 +3262,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,10 +3294,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176322</v>
+        <v>120176514</v>
       </c>
       <c r="B26" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582663</v>
+        <v>582518</v>
       </c>
       <c r="R26" t="n">
-        <v>7026088</v>
+        <v>7026110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120177433</v>
+        <v>120175885</v>
       </c>
       <c r="B13" t="n">
-        <v>74593</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582517</v>
+        <v>582678</v>
       </c>
       <c r="R13" t="n">
-        <v>7026141</v>
+        <v>7026025</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175885</v>
+        <v>120175644</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582678</v>
+        <v>582635</v>
       </c>
       <c r="R14" t="n">
-        <v>7026025</v>
+        <v>7025986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,6 +2058,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2074,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175644</v>
+        <v>120177433</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>74593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,25 +2101,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582635</v>
+        <v>582517</v>
       </c>
       <c r="R15" t="n">
-        <v>7025986</v>
+        <v>7026141</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,21 +2175,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120175892</v>
+        <v>120176065</v>
       </c>
       <c r="B22" t="n">
-        <v>79583</v>
+        <v>79652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582678</v>
+        <v>582672</v>
       </c>
       <c r="R22" t="n">
-        <v>7026025</v>
+        <v>7026027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120176065</v>
+        <v>120175892</v>
       </c>
       <c r="B23" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582672</v>
+        <v>582678</v>
       </c>
       <c r="R23" t="n">
-        <v>7026027</v>
+        <v>7026025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120176536</v>
+        <v>120176525</v>
       </c>
       <c r="B2" t="n">
-        <v>94334</v>
+        <v>79652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R2" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120175484</v>
+        <v>120177315</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582617</v>
+        <v>582517</v>
       </c>
       <c r="R4" t="n">
-        <v>7025987</v>
+        <v>7026141</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -961,19 +952,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120176305</v>
+        <v>120175584</v>
       </c>
       <c r="B5" t="n">
         <v>57336</v>
@@ -1036,7 +1017,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1048,7 +1029,7 @@
         <v>582645</v>
       </c>
       <c r="R5" t="n">
-        <v>7026059</v>
+        <v>7025976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1071,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175741</v>
+        <v>120176600</v>
       </c>
       <c r="B6" t="n">
-        <v>79527</v>
+        <v>90591</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582661</v>
+        <v>582505</v>
       </c>
       <c r="R6" t="n">
-        <v>7026021</v>
+        <v>7026082</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120175900</v>
+        <v>120176323</v>
       </c>
       <c r="B7" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582678</v>
+        <v>582522</v>
       </c>
       <c r="R7" t="n">
-        <v>7026025</v>
+        <v>7026104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,9 +1278,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176525</v>
+        <v>120175489</v>
       </c>
       <c r="B8" t="n">
-        <v>79652</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,38 +1329,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582518</v>
+        <v>582599</v>
       </c>
       <c r="R8" t="n">
-        <v>7026110</v>
+        <v>7025970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,9 +1395,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,19 +1422,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176085</v>
+        <v>120176679</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1458,12 +1469,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1472,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582532</v>
+        <v>582480</v>
       </c>
       <c r="R9" t="n">
-        <v>7026064</v>
+        <v>7026053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,22 +1538,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176600</v>
+        <v>120175885</v>
       </c>
       <c r="B10" t="n">
-        <v>90591</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,25 +1562,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1584,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582505</v>
+        <v>582678</v>
       </c>
       <c r="R10" t="n">
-        <v>7026082</v>
+        <v>7026025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120177419</v>
+        <v>120176505</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,38 +1664,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582515</v>
+        <v>582527</v>
       </c>
       <c r="R11" t="n">
-        <v>7026157</v>
+        <v>7026102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1731,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176323</v>
+        <v>120176085</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,38 +1780,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582522</v>
+        <v>582532</v>
       </c>
       <c r="R12" t="n">
-        <v>7026104</v>
+        <v>7026064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1843,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120175885</v>
+        <v>120177433</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>74593</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1901,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,13 +1929,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582678</v>
+        <v>582517</v>
       </c>
       <c r="R13" t="n">
-        <v>7026025</v>
+        <v>7026141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175644</v>
+        <v>120176065</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +2003,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582635</v>
+        <v>582672</v>
       </c>
       <c r="R14" t="n">
-        <v>7025986</v>
+        <v>7026027</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,21 +2077,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2089,10 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120177433</v>
+        <v>120176257</v>
       </c>
       <c r="B15" t="n">
-        <v>74593</v>
+        <v>79583</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,21 +2109,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,13 +2133,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582517</v>
+        <v>582663</v>
       </c>
       <c r="R15" t="n">
-        <v>7026141</v>
+        <v>7026088</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175489</v>
+        <v>120177419</v>
       </c>
       <c r="B16" t="n">
-        <v>56524</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,39 +2211,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582599</v>
+        <v>582515</v>
       </c>
       <c r="R16" t="n">
-        <v>7025970</v>
+        <v>7026157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2270,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2281,7 +2280,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120176679</v>
+        <v>120175900</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>79527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,42 +2319,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582480</v>
+        <v>582678</v>
       </c>
       <c r="R17" t="n">
-        <v>7026053</v>
+        <v>7026025</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,19 +2380,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176257</v>
+        <v>120175887</v>
       </c>
       <c r="B18" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2436,25 +2421,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582663</v>
+        <v>582692</v>
       </c>
       <c r="R18" t="n">
-        <v>7026088</v>
+        <v>7026050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,9 +2482,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,22 +2509,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120175748</v>
+        <v>120175892</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2538,25 +2533,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2566,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582659</v>
+        <v>582678</v>
       </c>
       <c r="R19" t="n">
-        <v>7026084</v>
+        <v>7026025</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,19 +2594,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,19 +2611,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120175887</v>
+        <v>120176514</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2678,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582692</v>
+        <v>582518</v>
       </c>
       <c r="R20" t="n">
-        <v>7026050</v>
+        <v>7026110</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,19 +2696,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,22 +2713,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120176505</v>
+        <v>120176536</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>94334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,42 +2737,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582527</v>
+        <v>582505</v>
       </c>
       <c r="R21" t="n">
-        <v>7026102</v>
+        <v>7026082</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,19 +2798,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,22 +2815,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120176065</v>
+        <v>120175644</v>
       </c>
       <c r="B22" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2878,25 +2839,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2906,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582672</v>
+        <v>582635</v>
       </c>
       <c r="R22" t="n">
-        <v>7026027</v>
+        <v>7025986</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,6 +2913,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2968,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120175892</v>
+        <v>120175484</v>
       </c>
       <c r="B23" t="n">
-        <v>79583</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,41 +2956,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582678</v>
+        <v>582617</v>
       </c>
       <c r="R23" t="n">
-        <v>7026025</v>
+        <v>7025987</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3041,9 +3026,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,22 +3053,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120177315</v>
+        <v>120176305</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,37 +3081,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582517</v>
+        <v>582645</v>
       </c>
       <c r="R24" t="n">
-        <v>7026141</v>
+        <v>7026059</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3143,9 +3143,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3160,22 +3170,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120175584</v>
+        <v>120175741</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>79527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3184,43 +3194,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582645</v>
+        <v>582661</v>
       </c>
       <c r="R25" t="n">
-        <v>7025976</v>
+        <v>7026021</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,24 +3255,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,19 +3272,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176514</v>
+        <v>120175748</v>
       </c>
       <c r="B26" t="n">
         <v>79623</v>
@@ -3334,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582518</v>
+        <v>582659</v>
       </c>
       <c r="R26" t="n">
-        <v>7026110</v>
+        <v>7026084</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,9 +3357,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,12 +3384,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120176525</v>
+        <v>120175892</v>
       </c>
       <c r="B2" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582518</v>
+        <v>582678</v>
       </c>
       <c r="R2" t="n">
-        <v>7026110</v>
+        <v>7026025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176322</v>
+        <v>120176679</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582663</v>
+        <v>582480</v>
       </c>
       <c r="R3" t="n">
-        <v>7026088</v>
+        <v>7026053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +854,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120177315</v>
+        <v>120176085</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +905,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582517</v>
+        <v>582532</v>
       </c>
       <c r="R4" t="n">
-        <v>7026141</v>
+        <v>7026064</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,9 +975,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +1002,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120175584</v>
+        <v>120175489</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +1030,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1017,7 +1050,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582645</v>
+        <v>582599</v>
       </c>
       <c r="R5" t="n">
-        <v>7025976</v>
+        <v>7025970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120176600</v>
+        <v>120175484</v>
       </c>
       <c r="B6" t="n">
-        <v>90591</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,41 +1143,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582505</v>
+        <v>582617</v>
       </c>
       <c r="R6" t="n">
-        <v>7026082</v>
+        <v>7025987</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,9 +1213,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120176323</v>
+        <v>120176322</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1264,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582522</v>
+        <v>582663</v>
       </c>
       <c r="R7" t="n">
-        <v>7026104</v>
+        <v>7026088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,19 +1325,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120175489</v>
+        <v>120175584</v>
       </c>
       <c r="B8" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,16 +1370,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,7 +1390,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582599</v>
+        <v>582645</v>
       </c>
       <c r="R8" t="n">
-        <v>7025970</v>
+        <v>7025976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1444,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176679</v>
+        <v>120175644</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,42 +1488,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582480</v>
+        <v>582635</v>
       </c>
       <c r="R9" t="n">
-        <v>7026053</v>
+        <v>7025986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,21 +1549,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1534,26 +1562,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120175885</v>
+        <v>120176536</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,25 +1605,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582678</v>
+        <v>582505</v>
       </c>
       <c r="R10" t="n">
-        <v>7026025</v>
+        <v>7026082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176505</v>
+        <v>120176514</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,42 +1707,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582527</v>
+        <v>582518</v>
       </c>
       <c r="R11" t="n">
-        <v>7026102</v>
+        <v>7026110</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,19 +1768,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,22 +1785,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176085</v>
+        <v>120176305</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,35 +1809,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1817,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582532</v>
+        <v>582645</v>
       </c>
       <c r="R12" t="n">
-        <v>7026064</v>
+        <v>7026059</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,22 +1902,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120177433</v>
+        <v>120175900</v>
       </c>
       <c r="B13" t="n">
-        <v>74593</v>
+        <v>79527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1930,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,13 +1954,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582517</v>
+        <v>582678</v>
       </c>
       <c r="R13" t="n">
-        <v>7026141</v>
+        <v>7026025</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120176065</v>
+        <v>120177433</v>
       </c>
       <c r="B14" t="n">
-        <v>79652</v>
+        <v>74593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,21 +2032,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2031,13 +2056,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582672</v>
+        <v>582517</v>
       </c>
       <c r="R14" t="n">
-        <v>7026027</v>
+        <v>7026141</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176257</v>
+        <v>120176065</v>
       </c>
       <c r="B15" t="n">
-        <v>79583</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2133,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582663</v>
+        <v>582672</v>
       </c>
       <c r="R15" t="n">
-        <v>7026088</v>
+        <v>7026027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120177419</v>
+        <v>120176323</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582515</v>
+        <v>582522</v>
       </c>
       <c r="R16" t="n">
-        <v>7026157</v>
+        <v>7026104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2280,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,22 +2320,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120175900</v>
+        <v>120176600</v>
       </c>
       <c r="B17" t="n">
-        <v>79527</v>
+        <v>90591</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2347,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582678</v>
+        <v>582505</v>
       </c>
       <c r="R17" t="n">
-        <v>7026025</v>
+        <v>7026082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120175887</v>
+        <v>120176505</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,38 +2446,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582692</v>
+        <v>582527</v>
       </c>
       <c r="R18" t="n">
-        <v>7026050</v>
+        <v>7026102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2494,7 +2523,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,7 +2550,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120175892</v>
+        <v>120176257</v>
       </c>
       <c r="B19" t="n">
         <v>79583</v>
@@ -2561,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582678</v>
+        <v>582663</v>
       </c>
       <c r="R19" t="n">
-        <v>7026025</v>
+        <v>7026088</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2652,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120176514</v>
+        <v>120175748</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2663,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582518</v>
+        <v>582659</v>
       </c>
       <c r="R20" t="n">
-        <v>7026110</v>
+        <v>7026084</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,9 +2725,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,22 +2752,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120176536</v>
+        <v>120176525</v>
       </c>
       <c r="B21" t="n">
-        <v>94334</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2780,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2804,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R21" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,7 +2866,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120175644</v>
+        <v>120175887</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -2867,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582635</v>
+        <v>582692</v>
       </c>
       <c r="R22" t="n">
-        <v>7025986</v>
+        <v>7026050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,11 +2939,21 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2913,41 +2962,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120175484</v>
+        <v>120175885</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2960,46 +2994,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582617</v>
+        <v>582678</v>
       </c>
       <c r="R23" t="n">
-        <v>7025987</v>
+        <v>7026025</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3026,19 +3051,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3053,22 +3068,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120176305</v>
+        <v>120177419</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,39 +3096,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582645</v>
+        <v>582515</v>
       </c>
       <c r="R24" t="n">
-        <v>7026059</v>
+        <v>7026157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3155,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3155,7 +3165,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3294,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120175748</v>
+        <v>120177315</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3300,21 +3310,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3324,13 +3334,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582659</v>
+        <v>582517</v>
       </c>
       <c r="R26" t="n">
-        <v>7026084</v>
+        <v>7026141</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3357,19 +3367,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,12 +3384,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176323</v>
+        <v>120176600</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>90591</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582522</v>
+        <v>582505</v>
       </c>
       <c r="R16" t="n">
-        <v>7026104</v>
+        <v>7026082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,19 +2293,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,22 +2310,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120176600</v>
+        <v>120176505</v>
       </c>
       <c r="B17" t="n">
-        <v>90591</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,38 +2334,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582505</v>
+        <v>582527</v>
       </c>
       <c r="R17" t="n">
-        <v>7026082</v>
+        <v>7026102</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,9 +2399,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,22 +2426,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176505</v>
+        <v>120176323</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2446,42 +2450,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582527</v>
+        <v>582522</v>
       </c>
       <c r="R18" t="n">
-        <v>7026102</v>
+        <v>7026104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,12 +2538,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175892</v>
+        <v>120175741</v>
       </c>
       <c r="B2" t="n">
-        <v>79583</v>
+        <v>79527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R2" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120176679</v>
+        <v>120175900</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>79527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582480</v>
+        <v>582678</v>
       </c>
       <c r="R3" t="n">
-        <v>7026053</v>
+        <v>7026025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,19 +850,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120176085</v>
+        <v>120175748</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582532</v>
+        <v>582659</v>
       </c>
       <c r="R4" t="n">
-        <v>7026064</v>
+        <v>7026084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120175489</v>
+        <v>120176305</v>
       </c>
       <c r="B5" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582599</v>
+        <v>582645</v>
       </c>
       <c r="R5" t="n">
-        <v>7025970</v>
+        <v>7026059</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175484</v>
+        <v>120176323</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,46 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582617</v>
+        <v>582522</v>
       </c>
       <c r="R6" t="n">
-        <v>7025987</v>
+        <v>7026104</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120176322</v>
+        <v>120177419</v>
       </c>
       <c r="B7" t="n">
-        <v>79652</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582663</v>
+        <v>582515</v>
       </c>
       <c r="R7" t="n">
-        <v>7026088</v>
+        <v>7026157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,9 +1293,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120175584</v>
+        <v>120177315</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,42 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582645</v>
+        <v>582517</v>
       </c>
       <c r="R8" t="n">
-        <v>7025976</v>
+        <v>7026141</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,24 +1405,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120175644</v>
+        <v>120175484</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,37 +1450,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582635</v>
+        <v>582617</v>
       </c>
       <c r="R9" t="n">
-        <v>7025986</v>
+        <v>7025987</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,11 +1516,21 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1562,41 +1539,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176536</v>
+        <v>120176514</v>
       </c>
       <c r="B10" t="n">
-        <v>94334</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,25 +1567,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1633,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582505</v>
+        <v>582518</v>
       </c>
       <c r="R10" t="n">
-        <v>7026082</v>
+        <v>7026110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120176514</v>
+        <v>120177433</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>74593</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,25 +1669,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,13 +1697,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582518</v>
+        <v>582517</v>
       </c>
       <c r="R11" t="n">
-        <v>7026110</v>
+        <v>7026141</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176305</v>
+        <v>120175892</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>79583</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,43 +1771,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582645</v>
+        <v>582678</v>
       </c>
       <c r="R12" t="n">
-        <v>7026059</v>
+        <v>7026025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,19 +1832,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120175900</v>
+        <v>120176065</v>
       </c>
       <c r="B13" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1954,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582678</v>
+        <v>582672</v>
       </c>
       <c r="R13" t="n">
-        <v>7026025</v>
+        <v>7026027</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120177433</v>
+        <v>120175584</v>
       </c>
       <c r="B14" t="n">
-        <v>74593</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,41 +1975,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582517</v>
+        <v>582645</v>
       </c>
       <c r="R14" t="n">
-        <v>7026141</v>
+        <v>7025976</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,9 +2041,24 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,22 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120176065</v>
+        <v>120175489</v>
       </c>
       <c r="B15" t="n">
-        <v>79652</v>
+        <v>56524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,38 +2097,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582672</v>
+        <v>582599</v>
       </c>
       <c r="R15" t="n">
-        <v>7026027</v>
+        <v>7025970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,9 +2163,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,22 +2190,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176600</v>
+        <v>120176679</v>
       </c>
       <c r="B16" t="n">
-        <v>90591</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,38 +2214,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582505</v>
+        <v>582480</v>
       </c>
       <c r="R16" t="n">
-        <v>7026082</v>
+        <v>7026053</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,9 +2279,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,22 +2306,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120176505</v>
+        <v>120175644</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,42 +2330,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582527</v>
+        <v>582635</v>
       </c>
       <c r="R17" t="n">
-        <v>7026102</v>
+        <v>7025986</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,21 +2391,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2422,23 +2404,38 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176323</v>
+        <v>120175887</v>
       </c>
       <c r="B18" t="n">
         <v>79623</v>
@@ -2478,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582522</v>
+        <v>582692</v>
       </c>
       <c r="R18" t="n">
-        <v>7026104</v>
+        <v>7026050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2523,7 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,22 +2535,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120176257</v>
+        <v>120176600</v>
       </c>
       <c r="B19" t="n">
-        <v>79583</v>
+        <v>90591</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,21 +2563,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2590,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582663</v>
+        <v>582505</v>
       </c>
       <c r="R19" t="n">
-        <v>7026088</v>
+        <v>7026082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120175748</v>
+        <v>120176257</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2664,25 +2661,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582659</v>
+        <v>582663</v>
       </c>
       <c r="R20" t="n">
-        <v>7026084</v>
+        <v>7026088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,19 +2722,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,22 +2739,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120176525</v>
+        <v>120175885</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2776,25 +2763,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2804,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582518</v>
+        <v>582678</v>
       </c>
       <c r="R21" t="n">
-        <v>7026110</v>
+        <v>7026025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2866,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120175887</v>
+        <v>120176505</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2878,38 +2865,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582692</v>
+        <v>582527</v>
       </c>
       <c r="R22" t="n">
-        <v>7026050</v>
+        <v>7026102</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2932,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2951,7 +2942,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120175885</v>
+        <v>120176525</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,25 +2981,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3018,10 +3009,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582678</v>
+        <v>582518</v>
       </c>
       <c r="R23" t="n">
-        <v>7026025</v>
+        <v>7026110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,10 +3071,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120177419</v>
+        <v>120176085</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,38 +3083,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582515</v>
+        <v>582532</v>
       </c>
       <c r="R24" t="n">
-        <v>7026157</v>
+        <v>7026064</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,22 +3180,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120175741</v>
+        <v>120176536</v>
       </c>
       <c r="B25" t="n">
-        <v>79527</v>
+        <v>94334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582661</v>
+        <v>582505</v>
       </c>
       <c r="R25" t="n">
-        <v>7026021</v>
+        <v>7026082</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120177315</v>
+        <v>120176322</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582517</v>
+        <v>582663</v>
       </c>
       <c r="R26" t="n">
-        <v>7026141</v>
+        <v>7026088</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120175741</v>
+        <v>120175900</v>
       </c>
       <c r="B2" t="n">
         <v>79527</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582661</v>
+        <v>582678</v>
       </c>
       <c r="R2" t="n">
-        <v>7026021</v>
+        <v>7026025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120175900</v>
+        <v>120176525</v>
       </c>
       <c r="B3" t="n">
-        <v>79527</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582678</v>
+        <v>582518</v>
       </c>
       <c r="R3" t="n">
-        <v>7026025</v>
+        <v>7026110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120175748</v>
+        <v>120176536</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582659</v>
+        <v>582505</v>
       </c>
       <c r="R4" t="n">
-        <v>7026084</v>
+        <v>7026082</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +952,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120176305</v>
+        <v>120176322</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582645</v>
+        <v>582663</v>
       </c>
       <c r="R5" t="n">
-        <v>7026059</v>
+        <v>7026088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,19 +1054,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120176323</v>
+        <v>120176679</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,38 +1095,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582522</v>
+        <v>582480</v>
       </c>
       <c r="R6" t="n">
-        <v>7026104</v>
+        <v>7026053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1162,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1172,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120177419</v>
+        <v>120175584</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,34 +1215,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582515</v>
+        <v>582645</v>
       </c>
       <c r="R7" t="n">
-        <v>7026157</v>
+        <v>7025976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1289,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120177315</v>
+        <v>120176065</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582517</v>
+        <v>582672</v>
       </c>
       <c r="R8" t="n">
-        <v>7026141</v>
+        <v>7026027</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120175484</v>
+        <v>120176323</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,46 +1439,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582617</v>
+        <v>582522</v>
       </c>
       <c r="R9" t="n">
-        <v>7025987</v>
+        <v>7026104</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176514</v>
+        <v>120176600</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>90591</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,25 +1547,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582518</v>
+        <v>582505</v>
       </c>
       <c r="R10" t="n">
-        <v>7026110</v>
+        <v>7026082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120177433</v>
+        <v>120175484</v>
       </c>
       <c r="B11" t="n">
-        <v>74593</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,38 +1649,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582517</v>
+        <v>582617</v>
       </c>
       <c r="R11" t="n">
-        <v>7026141</v>
+        <v>7025987</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,9 +1719,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,22 +1746,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120175892</v>
+        <v>120175741</v>
       </c>
       <c r="B12" t="n">
-        <v>79583</v>
+        <v>79527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582678</v>
+        <v>582661</v>
       </c>
       <c r="R12" t="n">
-        <v>7026025</v>
+        <v>7026021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120176065</v>
+        <v>120176305</v>
       </c>
       <c r="B13" t="n">
-        <v>79652</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,38 +1872,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582672</v>
+        <v>582645</v>
       </c>
       <c r="R13" t="n">
-        <v>7026027</v>
+        <v>7026059</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,9 +1938,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,22 +1965,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175584</v>
+        <v>120175885</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,39 +1993,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582645</v>
+        <v>582678</v>
       </c>
       <c r="R14" t="n">
-        <v>7025976</v>
+        <v>7026025</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,24 +2050,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål i gammal död Asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,22 +2067,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175489</v>
+        <v>120176257</v>
       </c>
       <c r="B15" t="n">
-        <v>56524</v>
+        <v>79583</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,43 +2091,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582599</v>
+        <v>582663</v>
       </c>
       <c r="R15" t="n">
-        <v>7025970</v>
+        <v>7026088</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,19 +2152,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,22 +2169,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120176679</v>
+        <v>120175748</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,42 +2193,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582480</v>
+        <v>582659</v>
       </c>
       <c r="R16" t="n">
-        <v>7026053</v>
+        <v>7026084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,7 +2256,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2266,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,12 +2281,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2435,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120175887</v>
+        <v>120176505</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,38 +2422,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582692</v>
+        <v>582527</v>
       </c>
       <c r="R18" t="n">
-        <v>7026050</v>
+        <v>7026102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2489,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2499,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,10 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120176600</v>
+        <v>120175892</v>
       </c>
       <c r="B19" t="n">
-        <v>90591</v>
+        <v>79583</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,21 +2542,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2587,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582505</v>
+        <v>582678</v>
       </c>
       <c r="R19" t="n">
-        <v>7026082</v>
+        <v>7026025</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2649,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120176257</v>
+        <v>120177419</v>
       </c>
       <c r="B20" t="n">
-        <v>79583</v>
+        <v>82321</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,25 +2640,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2689,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582663</v>
+        <v>582515</v>
       </c>
       <c r="R20" t="n">
-        <v>7026088</v>
+        <v>7026157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,9 +2701,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,22 +2728,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120175885</v>
+        <v>120176085</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,38 +2752,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582678</v>
+        <v>582532</v>
       </c>
       <c r="R21" t="n">
-        <v>7026025</v>
+        <v>7026064</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,9 +2822,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,22 +2849,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120176505</v>
+        <v>120176514</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2865,42 +2873,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582527</v>
+        <v>582518</v>
       </c>
       <c r="R22" t="n">
-        <v>7026102</v>
+        <v>7026110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,19 +2934,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,22 +2951,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120176525</v>
+        <v>120177433</v>
       </c>
       <c r="B23" t="n">
-        <v>79652</v>
+        <v>74593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2985,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3009,13 +3003,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582518</v>
+        <v>582517</v>
       </c>
       <c r="R23" t="n">
-        <v>7026110</v>
+        <v>7026141</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3071,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120176085</v>
+        <v>120175887</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,47 +3077,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582532</v>
+        <v>582692</v>
       </c>
       <c r="R24" t="n">
-        <v>7026064</v>
+        <v>7026050</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,7 +3140,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3165,7 +3150,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,22 +3165,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120176536</v>
+        <v>120175489</v>
       </c>
       <c r="B25" t="n">
-        <v>94334</v>
+        <v>56524</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,38 +3189,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582505</v>
+        <v>582599</v>
       </c>
       <c r="R25" t="n">
-        <v>7026082</v>
+        <v>7025970</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,9 +3255,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,22 +3282,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176322</v>
+        <v>120177315</v>
       </c>
       <c r="B26" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582663</v>
+        <v>582517</v>
       </c>
       <c r="R26" t="n">
-        <v>7026088</v>
+        <v>7026141</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120175484</v>
+        <v>120175741</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>79527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,50 +1649,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582617</v>
+        <v>582661</v>
       </c>
       <c r="R11" t="n">
-        <v>7025987</v>
+        <v>7026021</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,19 +1710,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,22 +1727,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120175741</v>
+        <v>120175484</v>
       </c>
       <c r="B12" t="n">
-        <v>79527</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,41 +1751,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582661</v>
+        <v>582617</v>
       </c>
       <c r="R12" t="n">
-        <v>7026021</v>
+        <v>7025987</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1831,9 +1821,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175748</v>
+        <v>120176505</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,38 +2193,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582659</v>
+        <v>582527</v>
       </c>
       <c r="R16" t="n">
-        <v>7026084</v>
+        <v>7026102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2260,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2266,7 +2270,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,19 +2285,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120175644</v>
+        <v>120175748</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2333,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582635</v>
+        <v>582659</v>
       </c>
       <c r="R17" t="n">
-        <v>7025986</v>
+        <v>7026084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,11 +2370,21 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2379,41 +2393,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176505</v>
+        <v>120175644</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,42 +2421,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582527</v>
+        <v>582635</v>
       </c>
       <c r="R18" t="n">
-        <v>7026102</v>
+        <v>7025986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,21 +2482,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2510,26 +2495,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120175892</v>
+        <v>120177419</v>
       </c>
       <c r="B19" t="n">
-        <v>79583</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2538,25 +2538,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582678</v>
+        <v>582515</v>
       </c>
       <c r="R19" t="n">
-        <v>7026025</v>
+        <v>7026157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,9 +2599,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,22 +2626,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120177419</v>
+        <v>120175892</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>79583</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2640,25 +2650,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582515</v>
+        <v>582678</v>
       </c>
       <c r="R20" t="n">
-        <v>7026157</v>
+        <v>7026025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,19 +2711,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,12 +2728,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120176514</v>
+        <v>120176600</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582518</v>
+        <v>582505</v>
       </c>
       <c r="R2" t="n">
-        <v>7026110</v>
+        <v>7026082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120175892</v>
+        <v>120177419</v>
       </c>
       <c r="B3" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582678</v>
+        <v>582515</v>
       </c>
       <c r="R3" t="n">
-        <v>7026025</v>
+        <v>7026157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120175741</v>
+        <v>120176536</v>
       </c>
       <c r="B4" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582661</v>
+        <v>582505</v>
       </c>
       <c r="R4" t="n">
-        <v>7026021</v>
+        <v>7026082</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120176505</v>
+        <v>120177315</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,41 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582527</v>
+        <v>582517</v>
       </c>
       <c r="R5" t="n">
-        <v>7026102</v>
+        <v>7026141</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,19 +1044,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120175489</v>
+        <v>120177433</v>
       </c>
       <c r="B6" t="n">
-        <v>56524</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,42 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582599</v>
+        <v>582517</v>
       </c>
       <c r="R6" t="n">
-        <v>7025970</v>
+        <v>7026141</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1141,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,67 +1158,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120176305</v>
+        <v>120175741</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582645</v>
+        <v>582661</v>
       </c>
       <c r="R7" t="n">
-        <v>7026059</v>
+        <v>7026021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,19 +1238,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,27 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120176257</v>
+        <v>120175900</v>
       </c>
       <c r="B8" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582663</v>
+        <v>582678</v>
       </c>
       <c r="R8" t="n">
-        <v>7026088</v>
+        <v>7026025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120176600</v>
+        <v>120175644</v>
       </c>
       <c r="B9" t="n">
-        <v>90591</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582505</v>
+        <v>582635</v>
       </c>
       <c r="R9" t="n">
-        <v>7026082</v>
+        <v>7025986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1445,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1535,37 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120176065</v>
+        <v>120175748</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582672</v>
+        <v>582659</v>
       </c>
       <c r="R10" t="n">
-        <v>7026027</v>
+        <v>7026084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,9 +1544,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,27 +1571,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120177419</v>
+        <v>120175885</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582515</v>
+        <v>582678</v>
       </c>
       <c r="R11" t="n">
-        <v>7026157</v>
+        <v>7026025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,19 +1651,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,66 +1668,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120176679</v>
+        <v>120175887</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582480</v>
+        <v>582692</v>
       </c>
       <c r="R12" t="n">
-        <v>7026053</v>
+        <v>7026050</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1750,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1838,7 +1760,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,15 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120175887</v>
+        <v>120176323</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582692</v>
+        <v>582522</v>
       </c>
       <c r="R13" t="n">
-        <v>7026050</v>
+        <v>7026104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1857,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1950,7 +1867,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,49 +1882,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120175900</v>
+        <v>120176514</v>
       </c>
       <c r="B14" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582678</v>
+        <v>582518</v>
       </c>
       <c r="R14" t="n">
-        <v>7026025</v>
+        <v>7026110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,15 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120175885</v>
+        <v>133126818</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,17 +2022,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Starrberget, Starrberget, Ång</t>
+          <t>Edsele, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582678</v>
+        <v>582502</v>
       </c>
       <c r="R15" t="n">
-        <v>7026025</v>
+        <v>7026105</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,12 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,49 +2076,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Emmy Ransgart</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Via Emmy Ransgart</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120175644</v>
+        <v>120176065</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582635</v>
+        <v>582672</v>
       </c>
       <c r="R16" t="n">
-        <v>7025986</v>
+        <v>7026027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,21 +2169,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2298,37 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120175748</v>
+        <v>120176322</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582659</v>
+        <v>582663</v>
       </c>
       <c r="R17" t="n">
-        <v>7026084</v>
+        <v>7026088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,19 +2253,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,27 +2270,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120176322</v>
+        <v>120176525</v>
       </c>
       <c r="B18" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582663</v>
+        <v>582518</v>
       </c>
       <c r="R18" t="n">
-        <v>7026088</v>
+        <v>7026110</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,16 +2382,11 @@
         <v>120175584</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2634,47 +2496,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120175484</v>
+        <v>120176305</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2683,13 +2536,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582617</v>
+        <v>582645</v>
       </c>
       <c r="R20" t="n">
-        <v>7025987</v>
+        <v>7026059</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2718,7 +2571,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2728,7 +2581,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,27 +2596,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120176536</v>
+        <v>120175489</v>
       </c>
       <c r="B21" t="n">
-        <v>94334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,34 +2619,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582505</v>
+        <v>582599</v>
       </c>
       <c r="R21" t="n">
-        <v>7026082</v>
+        <v>7025970</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,9 +2681,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,27 +2708,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120177315</v>
+        <v>120175484</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,34 +2731,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582517</v>
+        <v>582617</v>
       </c>
       <c r="R22" t="n">
-        <v>7026141</v>
+        <v>7025987</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2930,9 +2797,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,65 +2824,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120177433</v>
+        <v>120176085</v>
       </c>
       <c r="B23" t="n">
-        <v>74593</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582517</v>
+        <v>582532</v>
       </c>
       <c r="R23" t="n">
-        <v>7026141</v>
+        <v>7026064</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,9 +2913,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,62 +2940,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120176323</v>
+        <v>120176505</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582522</v>
+        <v>582527</v>
       </c>
       <c r="R24" t="n">
-        <v>7026104</v>
+        <v>7026102</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3026,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3146,7 +3036,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,62 +3051,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120176525</v>
+        <v>120176679</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582518</v>
+        <v>582480</v>
       </c>
       <c r="R25" t="n">
-        <v>7026110</v>
+        <v>7026053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,9 +3135,19 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,71 +3162,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120176085</v>
+        <v>120175892</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582532</v>
+        <v>582678</v>
       </c>
       <c r="R26" t="n">
-        <v>7026064</v>
+        <v>7026025</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,19 +3242,9 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,60 +3259,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133126818</v>
+        <v>120176257</v>
       </c>
       <c r="B27" t="n">
-        <v>80439</v>
+        <v>80392</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Edsele, Ång</t>
+          <t>Starrberget, Starrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582502</v>
+        <v>582663</v>
       </c>
       <c r="R27" t="n">
-        <v>7026105</v>
+        <v>7026088</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,12 +3336,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,12 +3356,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emmy Ransgart</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Emmy Ransgart</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 29918-2024 artfynd.xlsx
+++ b/artfynd/A 29918-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120177419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176536</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120177315</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120177433</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175741</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175900</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175644</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175748</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175885</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175887</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176323</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176514</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2085,6 +2155,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126818</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176065</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,6 +2359,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176322</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176525</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175584</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176305</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2717,6 +2817,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175489</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2949,6 +3059,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176085</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3060,6 +3175,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176505</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3171,6 +3291,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176679</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,6 +3393,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120175892</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,8 +3495,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120176257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>